--- a/sharedata/excel/B-兵营招募表(BarracksRecruitData).xlsx
+++ b/sharedata/excel/B-兵营招募表(BarracksRecruitData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="73">
   <si>
     <t>兵营招募表</t>
   </si>
@@ -127,10 +127,7 @@
     <t>ref(FactionData)</t>
   </si>
   <si>
-    <t>临时招募_临时小兵_1</t>
-  </si>
-  <si>
-    <t>临时小兵_1</t>
+    <t>盾卫步兵</t>
   </si>
   <si>
     <t>兵营-1级</t>
@@ -142,64 +139,118 @@
     <t>圣堂</t>
   </si>
   <si>
-    <t>临时招募_临时小兵_2</t>
-  </si>
-  <si>
-    <t>临时小兵_2</t>
+    <t>弓射手</t>
+  </si>
+  <si>
+    <t>兵营-3级</t>
+  </si>
+  <si>
+    <t>铁甲卫</t>
+  </si>
+  <si>
+    <t>兵营-6级</t>
+  </si>
+  <si>
+    <t>银翼狮鹫</t>
+  </si>
+  <si>
+    <t>兵营-10级</t>
+  </si>
+  <si>
+    <t>圣光修士</t>
+  </si>
+  <si>
+    <t>兵营-15级</t>
+  </si>
+  <si>
+    <t>金币//木材</t>
+  </si>
+  <si>
+    <t>20//5</t>
+  </si>
+  <si>
+    <t>铁戟骑士</t>
+  </si>
+  <si>
+    <t>兵营-20级</t>
+  </si>
+  <si>
+    <t>圣翼使徒</t>
+  </si>
+  <si>
+    <t>兵营-25级</t>
+  </si>
+  <si>
+    <t>骸弓兵</t>
   </si>
   <si>
     <t>墓园</t>
   </si>
   <si>
-    <t>临时招募_临时小兵_3</t>
-  </si>
-  <si>
-    <t>临时小兵_3</t>
+    <t>腐烂行尸</t>
+  </si>
+  <si>
+    <t>噬灵幽魂</t>
+  </si>
+  <si>
+    <t>吸血鬼</t>
+  </si>
+  <si>
+    <t>亡骨巫祭</t>
+  </si>
+  <si>
+    <t>黑骑士</t>
+  </si>
+  <si>
+    <t>骸骨巨龙</t>
+  </si>
+  <si>
+    <t>暗行斥候</t>
   </si>
   <si>
     <t>地牢</t>
   </si>
   <si>
-    <t>临时招募_临时小兵_4</t>
-  </si>
-  <si>
-    <t>临时小兵_4</t>
+    <t>血祭少女</t>
+  </si>
+  <si>
+    <t>牛斗士</t>
+  </si>
+  <si>
+    <t>幽暗女巫</t>
+  </si>
+  <si>
+    <t>蜥蜴掠骑</t>
+  </si>
+  <si>
+    <t>多头蛇蜥</t>
+  </si>
+  <si>
+    <t>暗影龙</t>
+  </si>
+  <si>
+    <t>藤牌兵</t>
   </si>
   <si>
     <t>神机</t>
   </si>
   <si>
-    <t>临时招募_临时小兵_5</t>
-  </si>
-  <si>
-    <t>临时小兵_5</t>
-  </si>
-  <si>
-    <t>兵营-2级</t>
-  </si>
-  <si>
-    <t>金币//木材</t>
-  </si>
-  <si>
-    <t>20//5</t>
-  </si>
-  <si>
-    <t>临时招募_临时小兵_6</t>
-  </si>
-  <si>
-    <t>临时小兵_6</t>
-  </si>
-  <si>
-    <t>临时招募_临时小兵_7</t>
-  </si>
-  <si>
-    <t>临时小兵_7</t>
-  </si>
-  <si>
-    <t>临时招募_临时小兵_8</t>
-  </si>
-  <si>
-    <t>临时小兵_8</t>
+    <t>鸟铳手</t>
+  </si>
+  <si>
+    <t>狼筅卫</t>
+  </si>
+  <si>
+    <t>神火飞鸦</t>
+  </si>
+  <si>
+    <t>火炮尉</t>
+  </si>
+  <si>
+    <t>连环铳骑</t>
+  </si>
+  <si>
+    <t>鎏金炎龙</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1250,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
@@ -1350,25 +1401,26 @@
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="6" t="str">
+        <f>H7&amp;"阵营_"&amp;D7</f>
+        <v>圣堂阵营_盾卫步兵</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I7" s="6">
         <v>1</v>
@@ -1376,25 +1428,26 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="6">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C8" s="6" t="str">
+        <f t="shared" ref="C8:C13" si="0">H8&amp;"阵营_"&amp;D8</f>
+        <v>圣堂阵营_弓射手</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G8" s="7">
         <v>10</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I8" s="6">
         <v>2</v>
@@ -1402,25 +1455,26 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="6">
-        <v>3</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>39</v>
+        <v>1003</v>
+      </c>
+      <c r="C9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>圣堂阵营_铁甲卫</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G9" s="7">
         <v>10</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I9" s="6">
         <v>3</v>
@@ -1428,25 +1482,26 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="6">
-        <v>4</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>1004</v>
+      </c>
+      <c r="C10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>圣堂阵营_银翼狮鹫</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G10" s="7">
         <v>10</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I10" s="6">
         <v>4</v>
@@ -1454,25 +1509,26 @@
     </row>
     <row r="11" spans="1:9">
       <c r="B11" s="6">
-        <v>5</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>45</v>
+        <v>1005</v>
+      </c>
+      <c r="C11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>圣堂阵营_圣光修士</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I11" s="6">
         <v>5</v>
@@ -1480,25 +1536,26 @@
     </row>
     <row r="12" spans="1:9">
       <c r="B12" s="6">
-        <v>6</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>50</v>
+        <v>1006</v>
+      </c>
+      <c r="C12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>圣堂阵营_铁戟骑士</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I12" s="6">
         <v>6</v>
@@ -1506,25 +1563,26 @@
     </row>
     <row r="13" spans="1:9">
       <c r="B13" s="6">
-        <v>7</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>52</v>
+        <v>1007</v>
+      </c>
+      <c r="C13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>圣堂阵营_圣翼使徒</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I13" s="6">
         <v>7</v>
@@ -1532,28 +1590,569 @@
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="6">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C14" s="6" t="str">
+        <f>H14&amp;"阵营_"&amp;D14</f>
+        <v>墓园阵营_骸弓兵</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="7">
+        <v>10</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="6">
+        <v>2002</v>
+      </c>
+      <c r="C15" s="6" t="str">
+        <f>H15&amp;"阵营_"&amp;D15</f>
+        <v>墓园阵营_腐烂行尸</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="7">
+        <v>10</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="6">
+        <v>2003</v>
+      </c>
+      <c r="C16" s="6" t="str">
+        <f>H16&amp;"阵营_"&amp;D16</f>
+        <v>墓园阵营_噬灵幽魂</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="7">
+        <v>10</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="6">
+        <v>2004</v>
+      </c>
+      <c r="C17" s="6" t="str">
+        <f>H17&amp;"阵营_"&amp;D17</f>
+        <v>墓园阵营_吸血鬼</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="7">
+        <v>10</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="6">
+        <v>2005</v>
+      </c>
+      <c r="C18" s="6" t="str">
+        <f>H18&amp;"阵营_"&amp;D18</f>
+        <v>墓园阵营_亡骨巫祭</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="6">
+        <v>2006</v>
+      </c>
+      <c r="C19" s="6" t="str">
+        <f>H19&amp;"阵营_"&amp;D19</f>
+        <v>墓园阵营_黑骑士</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="E19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="6">
+        <v>2007</v>
+      </c>
+      <c r="C20" s="6" t="str">
+        <f>H20&amp;"阵营_"&amp;D20</f>
+        <v>墓园阵营_骸骨巨龙</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="6" t="s">
+      <c r="F20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="6">
-        <v>8</v>
+      <c r="H20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="6">
+        <v>3001</v>
+      </c>
+      <c r="C21" s="6" t="str">
+        <f t="shared" ref="C21:C34" si="1">H21&amp;"阵营_"&amp;D21</f>
+        <v>地牢阵营_暗行斥候</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="7">
+        <v>10</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="6">
+        <v>3002</v>
+      </c>
+      <c r="C22" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>地牢阵营_血祭少女</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="7">
+        <v>10</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="6">
+        <v>3003</v>
+      </c>
+      <c r="C23" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>地牢阵营_牛斗士</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="7">
+        <v>10</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="6">
+        <v>3004</v>
+      </c>
+      <c r="C24" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>地牢阵营_幽暗女巫</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="7">
+        <v>10</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="6">
+        <v>3005</v>
+      </c>
+      <c r="C25" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>地牢阵营_蜥蜴掠骑</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="6">
+        <v>3006</v>
+      </c>
+      <c r="C26" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>地牢阵营_多头蛇蜥</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" s="6">
+        <v>3007</v>
+      </c>
+      <c r="C27" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>地牢阵营_暗影龙</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" s="6">
+        <v>4001</v>
+      </c>
+      <c r="C28" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>神机阵营_藤牌兵</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="7">
+        <v>10</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="6">
+        <v>4002</v>
+      </c>
+      <c r="C29" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>神机阵营_鸟铳手</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="7">
+        <v>10</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="6">
+        <v>4003</v>
+      </c>
+      <c r="C30" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>神机阵营_狼筅卫</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="7">
+        <v>10</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="6">
+        <v>4004</v>
+      </c>
+      <c r="C31" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>神机阵营_神火飞鸦</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" s="7">
+        <v>10</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="6">
+        <v>4005</v>
+      </c>
+      <c r="C32" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>神机阵营_火炮尉</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I32" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="6">
+        <v>4006</v>
+      </c>
+      <c r="C33" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>神机阵营_连环铳骑</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="6">
+        <v>4007</v>
+      </c>
+      <c r="C34" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>神机阵营_鎏金炎龙</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I34" s="6">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
